--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVIII/LTAIPT_A63F38A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVIII/LTAIPT_A63F38A.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -12,19 +12,21 @@
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
     <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
     <sheet name="Hidden_4" sheetId="5" r:id="rId5"/>
+    <sheet name="Hidden_5" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="Hidden_120">Hidden_1!$A$1:$A$3</definedName>
-    <definedName name="Hidden_229">Hidden_2!$A$1:$A$26</definedName>
-    <definedName name="Hidden_333">Hidden_3!$A$1:$A$41</definedName>
-    <definedName name="Hidden_440">Hidden_4!$A$1:$A$32</definedName>
+    <definedName name="Hidden_227">Hidden_2!$A$1:$A$2</definedName>
+    <definedName name="Hidden_330">Hidden_3!$A$1:$A$26</definedName>
+    <definedName name="Hidden_434">Hidden_4!$A$1:$A$41</definedName>
+    <definedName name="Hidden_541">Hidden_5!$A$1:$A$32</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="249">
   <si>
     <t>49002</t>
   </si>
@@ -146,6 +148,9 @@
     <t>436848</t>
   </si>
   <si>
+    <t>571942</t>
+  </si>
+  <si>
     <t>436825</t>
   </si>
   <si>
@@ -290,6 +295,9 @@
     <t>Segundo apellido</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
     <t>Correo electrónico</t>
   </si>
   <si>
@@ -353,7 +361,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>Beca universal para estudiantes de educación media superior "Benito Juárez"</t>
@@ -380,6 +388,12 @@
     <t>Alumnos vulnerables y con riesgo de abandonar la escuela</t>
   </si>
   <si>
+    <t>07/02/2023</t>
+  </si>
+  <si>
+    <t>21/07/2023</t>
+  </si>
+  <si>
     <t>Contrarrestar el abandono escolar</t>
   </si>
   <si>
@@ -389,12 +403,12 @@
     <t>Estudiantes</t>
   </si>
   <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/Beca_Universal_para_Estudiantes_de_Educacion_Media_Superior.pdf</t>
+  </si>
+  <si>
     <t>Económico</t>
   </si>
   <si>
-    <t>800</t>
-  </si>
-  <si>
     <t>Capturista</t>
   </si>
   <si>
@@ -446,37 +460,40 @@
     <t>Subdirección de Servicios Educativos</t>
   </si>
   <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Control%20Escolar/1er_Trimestre/</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20de%20Servicios%20Escolares/DOF%20-%20Diario%20Oficial%20de%20la%20Federaci%C3%B3n.pdf</t>
-  </si>
-  <si>
-    <t>EAAC5AA74B112C3B3FA4313C6075DDDD</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>21/02/2022</t>
-  </si>
-  <si>
-    <t>28/07/2022</t>
-  </si>
-  <si>
-    <t>14/07/2022</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 21 de febrero de 2022 al 28 de julio de 2022, el Colegio de Bachilleres del Estado de Tlaxcala, en el Programa de beca universal para estudiantes de educación media superior Benito Juárez, se encuentra de la siguiente manera: en la clave y denominación de partida presupuestal, los recursos son dispersados a los beneficiarios, directamente por la Coordinación Nacional de Becas para el Bienestar "Benito Juárez", por tanto no se tiene acceso a ello; los beneficiarios son ingresados por la dirección de cada plantel y aún se desconoce la manera en que haran llegar el recurso para  otorgarles su orden de pago y/o postulación y los jóvenes estudiantes acudan a realizar su cobro. Este proceso, depende del número de alumnos que se registren en la plataforma de becas, para después pasar a la validación que realiza la Coordinación Nacional de Becas para el Bienestar "Benito Juárez". No hay participación del Gobierno Estatal, sólo Federal. El monto es de $800.00 pesos mensuales no importando el género, el grado escolar ni el aprovechamiento académico. El presupuesto asignado al programa depende de la matrícula de alumnos vigente y puede variar cada semestre, por ciclo escolar.</t>
+    <t>Durante el periodo del  7 de febrero de 2023 al 21 de julio del 2023, el Colegio de Bachilleres del Estado de Tlaxcala, en el Programa de beca universal para estudiantes de educación media superior Benito Juárez, se encuentra de la siguiente manera: en la clave y denominación de partida presupuestal, los recursos son dispersados a los beneficiarios, directamente por la Coordinación Nacional de Becas para el Bienestar "Benito Juárez", por tanto no se tiene acceso a ello; los beneficiarios son ingresados por la dirección de cada plantel y aún se desconoce la manera en que haran llegar el recurso para  otorgarles su orden de pago y/o postulación y los jóvenes estudiantes acudan a realizar su cobro. Este proceso, depende del número de alumnos que se registren en la plataforma de becas, para después pasar a la validación que realiza la Coordinación Nacional de Becas para el Bienestar "Benito Juárez". No hay participación del Gobierno Estatal, sólo Federal. El monto es de $800.00 pesos mensuales no importando el género, el grado escolar ni el aprovechamiento académico. El presupuesto asignado al programa depende de la matrícula de alumnos vigente y puede variar cada semestre, por ciclo escolar.</t>
+  </si>
+  <si>
+    <t>684E134CA10453766D9C255DD95D3E4A</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>S311.</t>
+  </si>
+  <si>
+    <t>Programa Beca Universal para Estudiantes de Educación Media Superior Benito Juárez</t>
+  </si>
+  <si>
+    <t>875</t>
+  </si>
+  <si>
+    <t>Mujer</t>
+  </si>
+  <si>
+    <t>19/07/2023</t>
   </si>
   <si>
     <t>En especie</t>
   </si>
   <si>
     <t>Otros</t>
+  </si>
+  <si>
+    <t>Hombre</t>
   </si>
   <si>
     <t>Carretera</t>
@@ -1148,16 +1165,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AV8"/>
+  <dimension ref="A1:AW8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="65.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="73" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="40" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="61.7109375" bestFit="1" customWidth="1"/>
@@ -1173,40 +1190,41 @@
     <col min="20" max="20" width="153.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="158" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="153.7109375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="42.85546875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="33.5703125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="20" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="255" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="20" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1223,7 +1241,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -1238,7 +1256,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:48" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -1318,70 +1336,73 @@
         <v>6</v>
       </c>
       <c r="AB4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AC4" t="s">
         <v>6</v>
       </c>
       <c r="AD4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE4" t="s">
         <v>11</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>8</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>6</v>
       </c>
       <c r="AG4" t="s">
         <v>6</v>
       </c>
       <c r="AH4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI4" t="s">
         <v>11</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>8</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>6</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>8</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>6</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>8</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AO4" t="s">
         <v>6</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AP4" t="s">
         <v>11</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>6</v>
       </c>
       <c r="AQ4" t="s">
         <v>6</v>
       </c>
       <c r="AR4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AS4" t="s">
         <v>8</v>
       </c>
       <c r="AT4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AU4" t="s">
         <v>7</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AV4" t="s">
         <v>12</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AW4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:48" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -1523,10 +1544,13 @@
       <c r="AV5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1575,299 +1599,306 @@
       <c r="AT6" s="4"/>
       <c r="AU6" s="4"/>
       <c r="AV6" s="4"/>
-    </row>
-    <row r="7" spans="1:48" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="AW6" s="4"/>
+    </row>
+    <row r="7" spans="1:49" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG7" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AN7" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AQ7" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR7" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AS7" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AT7" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AU7" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AV7" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:48" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="AW7" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:49" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AE8" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AF8" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH8" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AJ8" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AK8" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL8" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AM8" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AN8" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AO8" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AP8" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AQ8" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AR8" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AS8" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="AT8" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="AU8" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AV8" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AW8" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="AB8" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="AC8" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="AD8" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="AE8" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AF8" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG8" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AH8" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="AI8" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AJ8" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK8" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AL8" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AM8" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AN8" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AO8" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AP8" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="AQ8" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="AR8" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="AS8" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AT8" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="AU8" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="AV8" s="2" t="s">
-        <v>148</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AV6"/>
+    <mergeCell ref="A6:AW6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1875,18 +1906,21 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="U8:U198">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="U8:U200">
       <formula1>Hidden_120</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AD8:AD198">
-      <formula1>Hidden_229</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AB8:AB200">
+      <formula1>Hidden_227</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AH8:AH198">
-      <formula1>Hidden_333</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AE8:AE200">
+      <formula1>Hidden_330</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AO8:AO198">
-      <formula1>Hidden_440</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AI8:AI200">
+      <formula1>Hidden_434</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AP8:AP200">
+      <formula1>Hidden_541</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1900,17 +1934,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -1920,137 +1954,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2060,212 +1974,137 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2275,167 +2114,382 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>217</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
